--- a/data/trans_bre/IP1002-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,42</t>
+          <t>0,0; 6,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 9,58</t>
+          <t>-1,47; 9,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 3,88</t>
+          <t>-3,49; 3,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 0,0</t>
+          <t>-5,06; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,61</t>
+          <t>-4,59; 0,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,71</t>
+          <t>-2,19; 3,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 0,07</t>
+          <t>-5,8; 0,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,43</t>
+          <t>-0,97; 2,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 3,24</t>
+          <t>-4,87; 3,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 5,82</t>
+          <t>-1,64; 5,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -0,76</t>
+          <t>-7,18; -0,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,06</t>
+          <t>-1,56; 3,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,53</t>
+          <t>0,0; 8,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 9,1</t>
+          <t>-3,23; 9,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,69; -1,19</t>
+          <t>-18,28; -0,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,23</t>
+          <t>0,0; 9,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,36</t>
+          <t>0,0; 6,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 1,44</t>
+          <t>-8,06; 2,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 2,34</t>
+          <t>-4,22; 2,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 0,0</t>
+          <t>-5,31; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,66</t>
+          <t>-2,23; 2,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,27</t>
+          <t>-2,11; 1,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 2,48</t>
+          <t>-6,6; 2,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 710,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-79,28; 99,38</t>
+          <t>-75,24; 120,29</t>
         </is>
       </c>
     </row>
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,89</t>
+          <t>-3,39; 1,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,0</t>
+          <t>-2,23; 0,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,49</t>
+          <t>-3,11; 1,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-85,29; 183,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-89,98; 282,53</t>
+          <t>-89,59; 273,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,12</t>
+          <t>-0,72; 1,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,29</t>
+          <t>-2,17; 0,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,58</t>
+          <t>-1,24; 0,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,12</t>
+          <t>-1,44; 0,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 155,5</t>
+          <t>-46,23; 175,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 21,2</t>
+          <t>-69,25; 19,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-68,12; 70,29</t>
+          <t>-64,23; 74,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 142,67</t>
+          <t>-65,92; 110,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,68</t>
+          <t>0,0; 7,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 9,49</t>
+          <t>-1,36; 9,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 3,9</t>
+          <t>-2,86; 4,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 0,0</t>
+          <t>-6,08; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,64</t>
+          <t>-4,86; 0,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,77</t>
+          <t>-2,22; 4,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 0,07</t>
+          <t>-5,8; 0,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 2,54</t>
+          <t>-1,03; 3,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 3,68</t>
+          <t>-4,84; 3,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,95</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 5,73</t>
+          <t>-1,74; 5,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -0,76</t>
+          <t>-6,79; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,21</t>
+          <t>-1,54; 3,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,72</t>
+          <t>0,0; 7,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 9,13</t>
+          <t>-3,21; 8,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -0,53</t>
+          <t>-18,54; -0,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,81</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 66,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,97</t>
+          <t>0,0; 7,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 2,53</t>
+          <t>-7,54; 1,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 2,27</t>
+          <t>-4,08; 2,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 0,0</t>
+          <t>-4,45; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,05</t>
+          <t>-1,61; 1,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,84</t>
+          <t>-2,4; 2,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,29</t>
+          <t>-1,86; 1,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 2,63</t>
+          <t>-6,59; 3,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 710,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-75,24; 120,29</t>
+          <t>-76,51; 157,37</t>
         </is>
       </c>
     </row>
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,95</t>
+          <t>-3,16; 1,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,0</t>
+          <t>-2,25; 0,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,53</t>
+          <t>-2,86; 1,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,04; 204,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-89,59; 273,46</t>
+          <t>-88,11; 270,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,22</t>
+          <t>-0,81; 1,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,27</t>
+          <t>-2,09; 0,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,64</t>
+          <t>-1,18; 0,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,89</t>
+          <t>-1,17; 1,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-46,23; 175,26</t>
+          <t>-50,99; 175,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 19,17</t>
+          <t>-67,84; 18,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-64,23; 74,74</t>
+          <t>-63,3; 88,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-65,92; 110,48</t>
+          <t>-60,81; 137,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-1,15</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,63</t>
+          <t>0,0; 5,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 9,93</t>
+          <t>-1,53; 9,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,11</t>
+          <t>-3,63; 3,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 0,0</t>
+          <t>-6,45; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>66,59%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 0,63</t>
+          <t>-4,41; 0,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,26</t>
+          <t>-2,23; 3,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 0,05</t>
+          <t>-5,28; 0,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,01</t>
+          <t>-0,77; 3,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 3,34</t>
+          <t>-4,86; 3,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 4,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 5,58</t>
+          <t>-1,36; 5,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 0,0</t>
+          <t>-7,29; -0,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,09</t>
+          <t>-1,56; 3,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,99</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 8,99</t>
+          <t>-1,89; 9,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,54; -0,89</t>
+          <t>-18,69; -1,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>0,0; 10,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,19</t>
+          <t>0,0; 6,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 1,55</t>
+          <t>-7,78; 1,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 2,28</t>
+          <t>-3,94; 2,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,0</t>
+          <t>-5,13; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-1,92</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-29,28%</t>
+          <t>-33,69%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,56</t>
+          <t>-1,62; 1,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,88</t>
+          <t>-2,16; 2,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,3</t>
+          <t>-2,13; 1,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 3,18</t>
+          <t>-7,67; 2,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-76,51; 157,37</t>
+          <t>-80,67; 85,3</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,88</t>
+          <t>-2,96; 1,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,0</t>
+          <t>-2,46; 0,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,45</t>
+          <t>-3,02; 1,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-84,04; 204,47</t>
+          <t>-85,29; 183,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-88,11; 270,45</t>
+          <t>-89,98; 282,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-6,64%</t>
+          <t>-2,76%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,19</t>
+          <t>-0,76; 1,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,31</t>
+          <t>-2,07; 0,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,7</t>
+          <t>-1,22; 0,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,01</t>
+          <t>-1,28; 1,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-50,99; 175,99</t>
+          <t>-50,8; 155,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-67,84; 18,37</t>
+          <t>-66,55; 21,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 88,97</t>
+          <t>-68,12; 70,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-60,81; 137,71</t>
+          <t>-63,21; 158,04</t>
         </is>
       </c>
     </row>
